--- a/docs/case_files/CASE_CYS.xlsx
+++ b/docs/case_files/CASE_CYS.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -776,6 +776,92 @@
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>BscScan top holders | contract verify L-28 | Nansen (LOCKED) | depth snap #2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE (R7 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>first_nn LSR (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>first_nn OI (fapi 30d)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>N/A-GAP dates (freshwatch)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-24, 2026-07-25, 2026-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>N/A-RETENTION rule</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Trước first_nn = N/A-RETENTION (store không cover, không collect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CORRECTIONS (R8 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Gap 24-26/07 nguồn store</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3 ngày freshwatch drop toàn universe — không sửa lịch sử</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schema v2.1 append cols 51-52</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>vol_spot_ext_usd + spot_ext_venue = CHƯA-TRA · chờ nhịp 2 R5</t>
         </is>
       </c>
     </row>
@@ -790,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX226"/>
+  <dimension ref="A1:AZ234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -896,6 +982,11 @@
           <t>B-2 DIAGNOSTIC FLAGS (dump analysis)</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>SPOT-EXT (v2.1 R4 21/08)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="13" t="inlineStr">
@@ -1146,6 +1237,16 @@
       <c r="AX2" s="13" t="inlineStr">
         <is>
           <t>flag_knife_crowd (gLSR↑&amp;ret&lt;-3%)</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>vol_spot_ext_usd</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>spot_ext_venue</t>
         </is>
       </c>
     </row>
@@ -1282,6 +1383,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -1418,6 +1529,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1554,6 +1675,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -1690,6 +1821,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -1826,6 +1967,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -1962,6 +2113,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -2098,6 +2259,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -2234,6 +2405,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -2370,6 +2551,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -2506,6 +2697,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -2642,6 +2843,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -2778,6 +2989,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -2918,6 +3139,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -3058,6 +3289,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -3196,6 +3437,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -3334,6 +3585,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -3472,6 +3733,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -3610,6 +3881,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -3748,6 +4029,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -3886,6 +4177,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -4024,6 +4325,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -4162,6 +4473,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4300,6 +4621,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -4438,6 +4769,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -4576,6 +4917,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -4714,6 +5065,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -4852,6 +5213,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -4990,6 +5361,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -5128,6 +5509,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -5266,6 +5657,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -5404,6 +5805,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -5542,6 +5953,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -5680,6 +6101,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -5818,6 +6249,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -5956,6 +6397,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -6094,6 +6545,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -6232,6 +6693,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -6370,6 +6841,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -6508,6 +6989,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -6650,6 +7141,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -6788,6 +7289,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
@@ -6930,6 +7441,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -7068,6 +7589,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
@@ -7206,6 +7737,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -7344,6 +7885,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -7482,6 +8033,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -7620,6 +8181,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
@@ -7758,6 +8329,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -7896,6 +8477,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
@@ -8034,6 +8625,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -8172,6 +8773,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
@@ -8310,6 +8921,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -8448,6 +9069,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
@@ -8590,6 +9221,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
@@ -8728,6 +9369,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
@@ -8866,6 +9517,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
@@ -9004,6 +9665,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
@@ -9146,6 +9817,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
@@ -9288,6 +9969,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
@@ -9430,6 +10121,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
@@ -9568,6 +10269,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
@@ -9706,6 +10417,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -9844,6 +10565,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
@@ -9982,6 +10713,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
@@ -10120,6 +10861,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
@@ -10262,6 +11013,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
@@ -10400,6 +11161,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
@@ -10538,6 +11309,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
@@ -10680,6 +11461,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
@@ -10818,6 +11609,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
@@ -10956,6 +11757,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
@@ -11094,6 +11905,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
@@ -11236,6 +12057,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
@@ -11374,6 +12205,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
@@ -11512,6 +12353,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
@@ -11650,6 +12501,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
@@ -11788,6 +12649,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
@@ -11926,6 +12797,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
@@ -12064,6 +12945,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
@@ -12202,6 +13093,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
@@ -12340,6 +13241,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
@@ -12478,6 +13389,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
@@ -12616,6 +13537,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
@@ -12754,6 +13685,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
@@ -12892,6 +13833,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
@@ -13030,6 +13981,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
@@ -13168,6 +14129,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
@@ -13306,6 +14277,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
@@ -13444,6 +14425,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
@@ -13582,6 +14573,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
@@ -13720,6 +14721,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
@@ -13858,6 +14869,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
@@ -13996,6 +15017,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
@@ -14134,6 +15165,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
@@ -14272,6 +15313,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
@@ -14410,6 +15461,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
@@ -14548,6 +15609,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
@@ -14686,6 +15757,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="inlineStr">
@@ -14824,6 +15905,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
@@ -14962,6 +16053,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="inlineStr">
@@ -15100,6 +16201,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
@@ -15238,6 +16349,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="inlineStr">
@@ -15376,6 +16497,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
@@ -15514,6 +16645,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="inlineStr">
@@ -15652,6 +16793,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
@@ -15790,6 +16941,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
@@ -15928,6 +17089,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
@@ -16066,6 +17237,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
@@ -16204,6 +17385,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
@@ -16342,6 +17533,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
@@ -16480,6 +17681,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
@@ -16618,6 +17829,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
@@ -16756,6 +17977,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
@@ -16894,6 +18125,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
@@ -17032,6 +18273,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
@@ -17170,6 +18421,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
@@ -17308,6 +18569,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
@@ -17446,6 +18717,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
@@ -17584,6 +18865,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
@@ -17722,6 +19013,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
@@ -17860,6 +19161,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
@@ -17998,6 +19309,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="inlineStr">
@@ -18136,6 +19457,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
@@ -18274,6 +19605,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="inlineStr">
@@ -18416,6 +19757,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
@@ -18554,6 +19905,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="14" t="inlineStr">
@@ -18692,6 +20053,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
@@ -18830,6 +20201,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="14" t="inlineStr">
@@ -18968,6 +20349,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
@@ -19106,6 +20497,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="14" t="inlineStr">
@@ -19244,6 +20645,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
@@ -19382,6 +20793,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
@@ -19520,6 +20941,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
@@ -19658,6 +21089,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
@@ -19796,6 +21237,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
@@ -19934,6 +21385,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="14" t="inlineStr">
@@ -20072,6 +21533,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
@@ -20210,6 +21681,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="14" t="inlineStr">
@@ -20348,6 +21829,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
@@ -20486,6 +21977,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="14" t="inlineStr">
@@ -20624,6 +22125,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
@@ -20762,6 +22273,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="14" t="inlineStr">
@@ -20900,6 +22421,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
@@ -21038,6 +22569,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="14" t="inlineStr">
@@ -21176,6 +22717,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
@@ -21314,6 +22865,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="14" t="inlineStr">
@@ -21456,6 +23017,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
@@ -21594,6 +23165,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="14" t="inlineStr">
@@ -21732,6 +23313,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
@@ -21874,6 +23465,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="14" t="inlineStr">
@@ -22012,6 +23613,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
@@ -22160,6 +23771,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="14" t="inlineStr">
@@ -22308,6 +23929,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
@@ -22458,6 +24089,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="14" t="inlineStr">
@@ -22612,6 +24253,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
@@ -22766,6 +24417,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="14" t="inlineStr">
@@ -22922,6 +24583,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
@@ -23078,6 +24749,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="14" t="inlineStr">
@@ -23234,6 +24915,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
@@ -23390,6 +25081,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="14" t="inlineStr">
@@ -23546,6 +25247,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
@@ -23702,6 +25413,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="14" t="inlineStr">
@@ -23862,6 +25583,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
@@ -24018,6 +25749,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="14" t="inlineStr">
@@ -24174,6 +25915,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
@@ -24330,6 +26081,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="14" t="inlineStr">
@@ -24486,6 +26247,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
@@ -24642,6 +26413,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="14" t="inlineStr">
@@ -24798,6 +26579,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
@@ -24954,6 +26745,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="14" t="inlineStr">
@@ -25110,6 +26911,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
@@ -25270,6 +27081,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="14" t="inlineStr">
@@ -25426,6 +27247,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
@@ -25582,6 +27413,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="14" t="inlineStr">
@@ -25738,6 +27579,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
@@ -25894,6 +27745,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="14" t="inlineStr">
@@ -26050,6 +27911,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
@@ -26206,6 +28077,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="14" t="inlineStr">
@@ -26362,6 +28243,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
@@ -26518,6 +28409,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="14" t="inlineStr">
@@ -26674,6 +28575,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
@@ -26830,6 +28741,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="inlineStr">
@@ -26986,6 +28907,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY185" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
@@ -27146,6 +29077,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="inlineStr">
@@ -27302,6 +29243,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
@@ -27458,6 +29409,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="14" t="inlineStr">
@@ -27614,6 +29575,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
@@ -27774,6 +29745,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="14" t="inlineStr">
@@ -27930,6 +29911,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
@@ -28086,6 +30077,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="14" t="inlineStr">
@@ -28242,6 +30243,16 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="inlineStr">
@@ -28398,6 +30409,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="14" t="inlineStr">
@@ -28558,6 +30579,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="14" t="inlineStr">
@@ -28714,6 +30745,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="14" t="inlineStr">
@@ -28870,6 +30911,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="14" t="inlineStr">
@@ -28960,7 +31011,7 @@
         <v>1.9386</v>
       </c>
       <c r="AD198" s="14" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9763216781752044</v>
       </c>
       <c r="AE198" s="14" t="inlineStr"/>
       <c r="AF198" s="14" t="inlineStr"/>
@@ -28999,7 +31050,7 @@
       </c>
       <c r="AP198" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ198" s="14" t="inlineStr"/>
@@ -29030,6 +31081,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="14" t="inlineStr">
@@ -29120,7 +31181,7 @@
         <v>1.9343</v>
       </c>
       <c r="AD199" s="14" t="n">
-        <v>0.6422</v>
+        <v>0.642154714913256</v>
       </c>
       <c r="AE199" s="14" t="inlineStr"/>
       <c r="AF199" s="14" t="inlineStr"/>
@@ -29159,7 +31220,7 @@
       </c>
       <c r="AP199" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ199" s="14" t="inlineStr"/>
@@ -29190,6 +31251,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="inlineStr">
@@ -29280,7 +31351,7 @@
         <v>1.6001</v>
       </c>
       <c r="AD200" s="14" t="n">
-        <v>1.0231</v>
+        <v>1.023075653361323</v>
       </c>
       <c r="AE200" s="14" t="inlineStr"/>
       <c r="AF200" s="14" t="inlineStr"/>
@@ -29319,7 +31390,7 @@
       </c>
       <c r="AP200" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ200" s="14" t="inlineStr"/>
@@ -29352,6 +31423,16 @@
       <c r="AX200" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -29444,7 +31525,7 @@
         <v>1.7027</v>
       </c>
       <c r="AD201" s="14" t="n">
-        <v>0.9452</v>
+        <v>0.9451579875718472</v>
       </c>
       <c r="AE201" s="14" t="inlineStr"/>
       <c r="AF201" s="14" t="inlineStr"/>
@@ -29483,7 +31564,7 @@
       </c>
       <c r="AP201" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ201" s="14" t="inlineStr"/>
@@ -29514,6 +31595,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="14" t="inlineStr">
@@ -29604,7 +31695,7 @@
         <v>1.742</v>
       </c>
       <c r="AD202" s="14" t="n">
-        <v>0.9523</v>
+        <v>0.9522338848668001</v>
       </c>
       <c r="AE202" s="14" t="inlineStr"/>
       <c r="AF202" s="14" t="inlineStr"/>
@@ -29643,7 +31734,7 @@
       </c>
       <c r="AP202" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ202" s="14" t="inlineStr"/>
@@ -29674,6 +31765,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="14" t="inlineStr">
@@ -29764,7 +31865,7 @@
         <v>1.7315</v>
       </c>
       <c r="AD203" s="14" t="n">
-        <v>0.9907</v>
+        <v>0.9907081446214162</v>
       </c>
       <c r="AE203" s="14" t="inlineStr"/>
       <c r="AF203" s="14" t="inlineStr"/>
@@ -29803,7 +31904,7 @@
       </c>
       <c r="AP203" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ203" s="14" t="inlineStr"/>
@@ -29834,6 +31935,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="14" t="inlineStr">
@@ -29924,7 +32035,7 @@
         <v>1.7278</v>
       </c>
       <c r="AD204" s="14" t="n">
-        <v>1.0233</v>
+        <v>1.023448431888238</v>
       </c>
       <c r="AE204" s="14" t="inlineStr"/>
       <c r="AF204" s="14" t="inlineStr"/>
@@ -29963,7 +32074,7 @@
       </c>
       <c r="AP204" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ204" s="14" t="inlineStr"/>
@@ -29994,6 +32105,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="14" t="inlineStr">
@@ -30086,7 +32207,7 @@
         <v>1.635</v>
       </c>
       <c r="AD205" s="14" t="n">
-        <v>0.9306</v>
+        <v>0.9306300755945141</v>
       </c>
       <c r="AE205" s="14" t="inlineStr"/>
       <c r="AF205" s="14" t="inlineStr"/>
@@ -30125,7 +32246,7 @@
       </c>
       <c r="AP205" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ205" s="14" t="inlineStr"/>
@@ -30156,6 +32277,16 @@
           <t>false</t>
         </is>
       </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="14" t="inlineStr">
@@ -30248,7 +32379,7 @@
         <v>1.6638</v>
       </c>
       <c r="AD206" s="14" t="n">
-        <v>0.9744</v>
+        <v>0.9743879135124754</v>
       </c>
       <c r="AE206" s="14" t="inlineStr"/>
       <c r="AF206" s="14" t="inlineStr"/>
@@ -30287,7 +32418,7 @@
       </c>
       <c r="AP206" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ206" s="14" t="inlineStr"/>
@@ -30316,6 +32447,16 @@
       <c r="AX206" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -30449,7 +32590,7 @@
       </c>
       <c r="AP207" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>fapi</t>
         </is>
       </c>
       <c r="AQ207" s="14" t="n">
@@ -30480,6 +32621,16 @@
       <c r="AX207" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -30613,7 +32764,7 @@
       </c>
       <c r="AP208" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>fapi</t>
         </is>
       </c>
       <c r="AQ208" s="14" t="n">
@@ -30644,6 +32795,16 @@
       <c r="AX208" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -30777,7 +32938,7 @@
       </c>
       <c r="AP209" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>fapi</t>
         </is>
       </c>
       <c r="AQ209" s="14" t="n">
@@ -30808,6 +32969,16 @@
       <c r="AX209" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -30941,7 +33112,7 @@
       </c>
       <c r="AP210" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ210" s="14" t="n">
@@ -30972,6 +33143,16 @@
       <c r="AX210" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -31105,7 +33286,7 @@
       </c>
       <c r="AP211" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ211" s="14" t="n">
@@ -31136,6 +33317,16 @@
       <c r="AX211" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -31269,7 +33460,7 @@
       </c>
       <c r="AP212" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ212" s="14" t="n">
@@ -31300,6 +33491,16 @@
       <c r="AX212" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -31433,7 +33634,7 @@
       </c>
       <c r="AP213" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ213" s="14" t="n">
@@ -31464,6 +33665,16 @@
       <c r="AX213" s="16" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -31597,7 +33808,7 @@
       </c>
       <c r="AP214" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ214" s="14" t="n">
@@ -31628,6 +33839,16 @@
       <c r="AX214" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -31761,7 +33982,7 @@
       </c>
       <c r="AP215" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ215" s="14" t="n">
@@ -31796,6 +34017,16 @@
       <c r="AX215" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -31929,7 +34160,7 @@
       </c>
       <c r="AP216" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ216" s="14" t="n">
@@ -31964,6 +34195,16 @@
       <c r="AX216" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -32097,7 +34338,7 @@
       </c>
       <c r="AP217" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ217" s="14" t="n">
@@ -32132,6 +34373,16 @@
       <c r="AX217" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -32265,7 +34516,7 @@
       </c>
       <c r="AP218" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ218" s="14" t="n">
@@ -32296,6 +34547,16 @@
       <c r="AX218" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -32429,7 +34690,7 @@
       </c>
       <c r="AP219" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ219" s="14" t="n">
@@ -32460,6 +34721,16 @@
       <c r="AX219" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -32593,7 +34864,7 @@
       </c>
       <c r="AP220" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ220" s="14" t="n">
@@ -32628,6 +34899,16 @@
       <c r="AX220" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -32761,7 +35042,7 @@
       </c>
       <c r="AP221" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ221" s="14" t="n">
@@ -32792,6 +35073,16 @@
       <c r="AX221" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -32925,7 +35216,7 @@
       </c>
       <c r="AP222" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ222" s="14" t="n">
@@ -32960,6 +35251,16 @@
       <c r="AX222" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -33093,7 +35394,7 @@
       </c>
       <c r="AP223" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ223" s="14" t="n">
@@ -33124,6 +35425,16 @@
       <c r="AX223" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -33257,7 +35568,7 @@
       </c>
       <c r="AP224" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ224" s="14" t="n">
@@ -33288,6 +35599,16 @@
       <c r="AX224" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -33421,7 +35742,7 @@
       </c>
       <c r="AP225" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ225" s="14" t="n">
@@ -33456,6 +35777,16 @@
       <c r="AX225" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>
@@ -33589,7 +35920,7 @@
       </c>
       <c r="AP226" s="14" t="inlineStr">
         <is>
-          <t>fapi_LSR_30d</t>
+          <t>freshwatch</t>
         </is>
       </c>
       <c r="AQ226" s="14" t="n">
@@ -33620,6 +35951,591 @@
       <c r="AX226" s="14" t="inlineStr">
         <is>
           <t>false</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1.33853333</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1.6752</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1.6995</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1.1024</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1.2137</v>
+      </c>
+      <c r="G227" t="n">
+        <v>197493295.6</v>
+      </c>
+      <c r="H227" t="n">
+        <v>50.4987</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.00029859</v>
+      </c>
+      <c r="J227" t="n">
+        <v>9.652e-05</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0.00045809</v>
+      </c>
+      <c r="L227" t="n">
+        <v>6</v>
+      </c>
+      <c r="M227" t="n">
+        <v>31147268.04349698</v>
+      </c>
+      <c r="N227" t="n">
+        <v>18596541</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>0.8431999999999999</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>1.0222</v>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1.16246667</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1.2138</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1.4431</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="F228" t="n">
+        <v>1.1973</v>
+      </c>
+      <c r="G228" t="n">
+        <v>250699571.32</v>
+      </c>
+      <c r="H228" t="n">
+        <v>50.6148</v>
+      </c>
+      <c r="I228" t="n">
+        <v>-0.00020633</v>
+      </c>
+      <c r="J228" t="n">
+        <v>-0.00154031</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0.00027389</v>
+      </c>
+      <c r="L228" t="n">
+        <v>6</v>
+      </c>
+      <c r="M228" t="n">
+        <v>19681568.40418836</v>
+      </c>
+      <c r="N228" t="n">
+        <v>16240447</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>0.9077</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>0.6284</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>0.6852</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>1.0216</v>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1.16376667</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1.1973</v>
+      </c>
+      <c r="D229" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.8043</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="G229" t="n">
+        <v>484746920.82</v>
+      </c>
+      <c r="H229" t="n">
+        <v>50.638</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.00022836</v>
+      </c>
+      <c r="J229" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0.0008604</v>
+      </c>
+      <c r="L229" t="n">
+        <v>6</v>
+      </c>
+      <c r="M229" t="n">
+        <v>16328462.824304</v>
+      </c>
+      <c r="N229" t="n">
+        <v>13624760</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>0.7937</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>0.6683</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>0.8073</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>1.0179</v>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0.7658</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.8472</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.8821</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0.6166</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.7987</v>
+      </c>
+      <c r="G230" t="n">
+        <v>323397331.75</v>
+      </c>
+      <c r="H230" t="n">
+        <v>50.3849</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0.00021525</v>
+      </c>
+      <c r="J230" t="n">
+        <v>-0.00014249</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0.0015084</v>
+      </c>
+      <c r="L230" t="n">
+        <v>6</v>
+      </c>
+      <c r="M230" t="n">
+        <v>14163347.49242288</v>
+      </c>
+      <c r="N230" t="n">
+        <v>16721734</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>0.9153</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>1.0148</v>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>0.58753333</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.7987</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.8686</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0.4332</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="G231" t="n">
+        <v>202757970.39</v>
+      </c>
+      <c r="H231" t="n">
+        <v>49.2852</v>
+      </c>
+      <c r="I231" t="n">
+        <v>7.730000000000001e-06</v>
+      </c>
+      <c r="J231" t="n">
+        <v>-0.00014914</v>
+      </c>
+      <c r="K231" t="n">
+        <v>6.121000000000001e-05</v>
+      </c>
+      <c r="L231" t="n">
+        <v>6</v>
+      </c>
+      <c r="M231" t="n">
+        <v>12955094.87597688</v>
+      </c>
+      <c r="N231" t="n">
+        <v>16220354</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>0.8426</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>0.7135</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>0.8409</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>freshwatch</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0.50553333</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.5522</v>
+      </c>
+      <c r="E232" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.5194</v>
+      </c>
+      <c r="G232" t="n">
+        <v>143611066.75</v>
+      </c>
+      <c r="H232" t="n">
+        <v>50.0204</v>
+      </c>
+      <c r="I232" t="n">
+        <v>3.416e-05</v>
+      </c>
+      <c r="J232" t="n">
+        <v>-1.443e-05</v>
+      </c>
+      <c r="K232" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="L232" t="n">
+        <v>6</v>
+      </c>
+      <c r="M232" t="n">
+        <v>9274801.207451779</v>
+      </c>
+      <c r="N232" t="n">
+        <v>20125651</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>1.0432</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>1.0942</v>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>fapi</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0.56363333</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.5194</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.6105</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0.4966</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="G233" t="n">
+        <v>87658199.40000001</v>
+      </c>
+      <c r="H233" t="n">
+        <v>49.132</v>
+      </c>
+      <c r="I233" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="J233" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K233" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="L233" t="n">
+        <v>6</v>
+      </c>
+      <c r="M233" t="n">
+        <v>10110427.7208</v>
+      </c>
+      <c r="N233" t="n">
+        <v>19458098</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>1.0234</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>1.0899</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>1.1195</v>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>fapi</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0.5726333300000001</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.6366000000000001</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.5499000000000001</v>
+      </c>
+      <c r="G234" t="n">
+        <v>37880435.67</v>
+      </c>
+      <c r="H234" t="n">
+        <v>48.0039</v>
+      </c>
+      <c r="I234" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="J234" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K234" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="L234" t="n">
+        <v>6</v>
+      </c>
+      <c r="M234" t="n">
+        <v>9984360.525281381</v>
+      </c>
+      <c r="N234" t="n">
+        <v>17110261</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>1.0423</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>1.0934</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>1.1048</v>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>fapi</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>CHƯA-TRA</t>
         </is>
       </c>
     </row>

--- a/docs/case_files/CASE_CYS.xlsx
+++ b/docs/case_files/CASE_CYS.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -862,6 +862,80 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>vol_spot_ext_usd + spot_ext_venue = CHƯA-TRA · chờ nhịp 2 R5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>META (V5 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>v2+ext-20260821 (v2 cols 1-50 + R4 append cols 51-52 CHƯA-TRA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>consumer_rule</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Consumer đọc theo HEADER row 2 field names (không hardcode col index). Cols 42+ append-only per L-57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE UPDATE (V4 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>lsr_null_dates (151)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01-01, 2026-01-02, 2026-01-03, 2026-01-04, 2026-01-05, 2026-01-06, 2026-01-07, 2026-01-08, 2026-01-09, 2026-01-10, 2026-01-11, 2026-01-12, 2026-01-13, 2026-01-14, 2026-01-15, 2026-01-16, 2026-01-17, 2026-01-18, 2026-01-19, 2026-01-20, 2026-01-21, 2026-01-22, 2026-01-23, 2026-01-24, 2026-01-25, 2026-01-26, 2026-01-27, 2026-01-28, 2026-01-29, 2026-01-30, 2026-01-31, 2026-02-01, 2026-02-02, 2026-02-03, 2026-02-04, 2026-02-05, 2026-02-06, 2026-02-07, 2026-02-08, 2026-02-09, 2026-02-10, 2026-02-11, 2026-02-12, 2026-02-13, 2026-02-14, 2026-02-15, 2026-02-16, 2026-02-17, 2026-02-18, 2026-02-19, 2026-02-20, 2026-02-21, 2026-02-22, 2026-02-23, 2026-02-24, 2026-02-25, 2026-02-26, 2026-02-27, 2026-02-28, 2026-03-01, 2026-03-02, 2026-03-03, 2026-03-04, 2026-03-05, 2026-03-06, 2026-03-07, 2026-03-08, 2026-03-09, 2026-03-10, 2026-03-11, 2026-03-12, 2026-03-13, 2026-03-14, 2026-03-15, 2026-03-16, 2026-03-17, 2026-03-18, 2026-03-19, 2026-03-20, 2026-03-21, 2026-03-22, 2026-03-23, 2026-03-24, 2026-03-25, 2026-03-26, 2026-03-27, 2026-03-28, 2026-03-29, 2026-03-30, 2026-03-31, 2026-04-01, 2026-04-02, 2026-04-03, 2026-04-04, 2026-04-05, 2026-04-06, 2026-04-07, 2026-04-08, 2026-04-09, 2026-04-10, 2026-04-11, 2026-04-12, 2026-04-13, 2026-04-14, 2026-04-15, 2026-04-16, 2026-04-17, 2026-04-18, 2026-04-19, 2026-04-20, 2026-04-21, 2026-04-22, 2026-04-23, 2026-04-24, 2026-04-25, 2026-04-26, 2026-04-27, 2026-04-28, 2026-04-29, 2026-04-30, 2026-05-01, 2026-05-02, 2026-05-03, 2026-05-04, 2026-05-05, 2026-05-06, 2026-05-07, 2026-05-08, 2026-05-09, 2026-05-10, 2026-05-11, 2026-05-12, 2026-05-13, 2026-05-14, 2026-05-15, 2026-05-16, 2026-05-17, 2026-05-18, 2026-05-19, 2026-05-20, 2026-05-21, 2026-05-22, 2026-05-23, 2026-05-24, 2026-05-25, 2026-05-26, 2026-05-27, 2026-05-28, 2026-05-29, 2026-05-30, 2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OI first_nn (real)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OI last_nn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
